--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.21252051575546</v>
+        <v>2.309534583810262</v>
       </c>
       <c r="D2" t="n">
-        <v>14.73612494198757</v>
+        <v>2.394620303072979</v>
       </c>
       <c r="E2" t="n">
-        <v>9.341328670672992</v>
+        <v>1.517965908984361</v>
       </c>
       <c r="F2" t="n">
-        <v>9.519763831797697</v>
+        <v>1.546961622667126</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.26496800842737</v>
+        <v>2.318057301369448</v>
       </c>
       <c r="D3" t="n">
-        <v>13.24588299237032</v>
+        <v>2.152455986260177</v>
       </c>
       <c r="E3" t="n">
-        <v>9.341328670672992</v>
+        <v>1.517965908984361</v>
       </c>
       <c r="F3" t="n">
-        <v>9.519763831797697</v>
+        <v>1.546961622667126</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.05464275159478</v>
+        <v>5.533879447134153</v>
       </c>
       <c r="D4" t="n">
-        <v>34.14419104908033</v>
+        <v>5.548431045475553</v>
       </c>
       <c r="E4" t="n">
-        <v>9.341328670672992</v>
+        <v>1.517965908984361</v>
       </c>
       <c r="F4" t="n">
-        <v>9.519763831797697</v>
+        <v>1.546961622667126</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
